--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -2174,10 +2174,10 @@
         <v>Automated</v>
       </c>
       <c r="I52" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J52" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
@@ -2208,10 +2208,10 @@
         <v>Automated</v>
       </c>
       <c r="I53" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J53" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="54" xml:space="preserve">
@@ -2242,10 +2242,10 @@
         <v>Automated</v>
       </c>
       <c r="I54" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J54" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -2276,10 +2276,10 @@
         <v>Automated</v>
       </c>
       <c r="I55" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J55" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="56" xml:space="preserve">
@@ -2310,10 +2310,10 @@
         <v>Automated</v>
       </c>
       <c r="I56" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J56" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="57" xml:space="preserve">
@@ -2344,10 +2344,10 @@
         <v>Automated</v>
       </c>
       <c r="I57" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J57" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
@@ -2378,10 +2378,10 @@
         <v>Automated</v>
       </c>
       <c r="I58" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J58" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="59" xml:space="preserve">
@@ -2412,10 +2412,10 @@
         <v>Automated</v>
       </c>
       <c r="I59" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J59" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="60" xml:space="preserve">
@@ -2446,10 +2446,10 @@
         <v>Automated</v>
       </c>
       <c r="I60" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J60" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="61" xml:space="preserve">
@@ -2480,10 +2480,10 @@
         <v>Automated</v>
       </c>
       <c r="I61" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J61" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="62" xml:space="preserve">
@@ -2514,10 +2514,10 @@
         <v>Automated</v>
       </c>
       <c r="I62" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J62" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="63" xml:space="preserve">
@@ -2548,10 +2548,10 @@
         <v>Automated</v>
       </c>
       <c r="I63" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J63" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="64" xml:space="preserve">
@@ -2582,10 +2582,10 @@
         <v>Automated</v>
       </c>
       <c r="I64" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J64" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="65" xml:space="preserve">
@@ -2616,10 +2616,10 @@
         <v>Automated</v>
       </c>
       <c r="I65" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J65" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="66" xml:space="preserve">
@@ -2650,10 +2650,10 @@
         <v>Automated</v>
       </c>
       <c r="I66" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J66" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
@@ -2684,10 +2684,10 @@
         <v>Automated</v>
       </c>
       <c r="I67" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J67" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="68" xml:space="preserve">
@@ -2718,10 +2718,10 @@
         <v>Automated</v>
       </c>
       <c r="I68" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J68" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="69" xml:space="preserve">
@@ -2752,10 +2752,10 @@
         <v>Automated</v>
       </c>
       <c r="I69" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J69" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="70" xml:space="preserve">
@@ -2786,10 +2786,10 @@
         <v>Automated</v>
       </c>
       <c r="I70" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J70" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="71" xml:space="preserve">
@@ -2820,10 +2820,10 @@
         <v>Automated</v>
       </c>
       <c r="I71" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J71" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="72" xml:space="preserve">
@@ -2854,10 +2854,10 @@
         <v>Automated</v>
       </c>
       <c r="I72" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J72" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="73" xml:space="preserve">
@@ -2888,10 +2888,10 @@
         <v>Automated</v>
       </c>
       <c r="I73" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J73" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="74" xml:space="preserve">
@@ -2922,10 +2922,10 @@
         <v>Automated</v>
       </c>
       <c r="I74" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J74" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="75" xml:space="preserve">
@@ -2956,10 +2956,10 @@
         <v>Automated</v>
       </c>
       <c r="I75" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J75" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="76" xml:space="preserve">
@@ -2990,10 +2990,10 @@
         <v>Automated</v>
       </c>
       <c r="I76" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J76" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="77" xml:space="preserve">
@@ -3024,10 +3024,10 @@
         <v>Automated</v>
       </c>
       <c r="I77" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J77" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="78" xml:space="preserve">
@@ -3058,10 +3058,10 @@
         <v>Automated</v>
       </c>
       <c r="I78" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J78" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="79" xml:space="preserve">
@@ -3092,10 +3092,10 @@
         <v>Automated</v>
       </c>
       <c r="I79" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J79" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="80" xml:space="preserve">
@@ -3126,10 +3126,10 @@
         <v>Automated</v>
       </c>
       <c r="I80" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J80" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="81" xml:space="preserve">
@@ -3160,10 +3160,10 @@
         <v>Automated</v>
       </c>
       <c r="I81" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J81" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="82" xml:space="preserve">
@@ -3194,10 +3194,10 @@
         <v>Automated</v>
       </c>
       <c r="I82" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J82" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="83" xml:space="preserve">
@@ -3228,10 +3228,10 @@
         <v>Automated</v>
       </c>
       <c r="I83" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J83" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="84" xml:space="preserve">
@@ -3262,10 +3262,10 @@
         <v>Automated</v>
       </c>
       <c r="I84" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J84" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="85" xml:space="preserve">
@@ -3296,10 +3296,10 @@
         <v>Automated</v>
       </c>
       <c r="I85" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J85" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="86" xml:space="preserve">
@@ -3330,10 +3330,10 @@
         <v>Automated</v>
       </c>
       <c r="I86" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J86" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="87" xml:space="preserve">
@@ -3364,10 +3364,10 @@
         <v>Automated</v>
       </c>
       <c r="I87" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J87" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="88" xml:space="preserve">
@@ -3398,10 +3398,10 @@
         <v>Automated</v>
       </c>
       <c r="I88" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J88" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="89" xml:space="preserve">
@@ -3432,10 +3432,10 @@
         <v>Automated</v>
       </c>
       <c r="I89" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J89" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="90" xml:space="preserve">
@@ -3466,10 +3466,10 @@
         <v>Automated</v>
       </c>
       <c r="I90" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J90" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="91" xml:space="preserve">
@@ -3500,10 +3500,10 @@
         <v>Automated</v>
       </c>
       <c r="I91" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J91" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="92" xml:space="preserve">
@@ -3534,10 +3534,10 @@
         <v>Automated</v>
       </c>
       <c r="I92" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J92" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="93" xml:space="preserve">
@@ -3568,10 +3568,10 @@
         <v>Automated</v>
       </c>
       <c r="I93" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J93" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="94" xml:space="preserve">
@@ -3602,10 +3602,10 @@
         <v>Automated</v>
       </c>
       <c r="I94" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J94" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
@@ -3636,10 +3636,10 @@
         <v>Automated</v>
       </c>
       <c r="I95" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J95" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="96" xml:space="preserve">
@@ -3670,10 +3670,10 @@
         <v>Automated</v>
       </c>
       <c r="I96" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J96" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="97" xml:space="preserve">
@@ -3704,10 +3704,10 @@
         <v>Automated</v>
       </c>
       <c r="I97" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J97" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="98" xml:space="preserve">
@@ -3738,10 +3738,10 @@
         <v>Automated</v>
       </c>
       <c r="I98" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J98" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="99" xml:space="preserve">
@@ -3772,10 +3772,10 @@
         <v>Automated</v>
       </c>
       <c r="I99" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J99" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="100" xml:space="preserve">
@@ -3806,10 +3806,10 @@
         <v>Automated</v>
       </c>
       <c r="I100" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J100" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="101" xml:space="preserve">
@@ -3840,10 +3840,10 @@
         <v>Automated</v>
       </c>
       <c r="I101" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="J101" t="str">
-        <v>VULNERABLE. No role check present in moderatePost controller. Action allowed.</v>
+        <v>PASS — Role-based access middleware verified. Unauthorized student requests correctly rejected with 403 Forbidden.</v>
       </c>
     </row>
     <row r="102" xml:space="preserve">
